--- a/Data/Rules/Winnie Lou Rules Matrix.xlsx
+++ b/Data/Rules/Winnie Lou Rules Matrix.xlsx
@@ -778,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="b">
         <v>0</v>
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:41">
@@ -1242,10 +1242,10 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -1260,10 +1260,10 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
@@ -1278,10 +1278,10 @@
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="b">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="AO6">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:41">
@@ -1367,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="R7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -1385,10 +1385,10 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
@@ -1403,10 +1403,10 @@
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="b">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="AO7">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:41">
@@ -1492,10 +1492,10 @@
         <v>0</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -1510,10 +1510,10 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
@@ -1528,10 +1528,10 @@
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="b">
         <v>0</v>
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AO8">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:41">
@@ -1635,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
@@ -1653,10 +1653,10 @@
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="b">
         <v>0</v>
@@ -1686,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="AO9">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:41">
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="b">
         <v>0</v>
@@ -1811,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="AO10">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:41">
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="b">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:41">
@@ -2153,10 +2153,10 @@
         <v>0</v>
       </c>
       <c r="AD13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="b">
         <v>0</v>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="AO13">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:41">
@@ -2278,10 +2278,10 @@
         <v>0</v>
       </c>
       <c r="AD14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="b">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:41">
@@ -2403,10 +2403,10 @@
         <v>0</v>
       </c>
       <c r="AD15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF15" t="b">
         <v>0</v>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:41">
@@ -2528,10 +2528,10 @@
         <v>0</v>
       </c>
       <c r="AD16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="b">
         <v>0</v>
@@ -2561,7 +2561,7 @@
         <v>0</v>
       </c>
       <c r="AO16">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
